--- a/test/accuracy/round11_accuracy.xlsx
+++ b/test/accuracy/round11_accuracy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24960" windowHeight="12720" activeTab="1"/>
+    <workbookView windowWidth="12480" windowHeight="12720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="表一_个人正确率" sheetId="1" r:id="rId1"/>
@@ -1350,10 +1350,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="6"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1380,8 +1380,12 @@
       <c r="D2" s="2">
         <v>0.904494845360825</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="F2" s="2">
+        <v>0.7618</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1394,8 +1398,12 @@
       <c r="D3" s="2">
         <v>0.944244897959184</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="F3" s="2">
+        <v>0.8003</v>
+      </c>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -1408,8 +1416,12 @@
       <c r="D4" s="2">
         <v>0.933325301204819</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="F4" s="2">
+        <v>0.7954</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1422,8 +1434,12 @@
       <c r="D5" s="2">
         <v>0.919867256637168</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="F5" s="2">
+        <v>0.7867</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1436,8 +1452,12 @@
       <c r="D6" s="2">
         <v>0.911546252532073</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="F6" s="2">
+        <v>0.7782</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1450,8 +1470,12 @@
       <c r="D7" s="2">
         <v>0.926456211812627</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="F7" s="2">
+        <v>0.7912</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1464,6 +1488,10 @@
       <c r="D8" s="2">
         <v>0.92904702970297</v>
       </c>
+      <c r="F8" s="2">
+        <v>0.7948</v>
+      </c>
+      <c r="G8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
